--- a/diseases/d049/2015-2019.xlsx
+++ b/diseases/d049/2015-2019.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1661,6 +1671,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1806,6 +1821,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2546,6 +2566,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2691,6 +2716,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3431,6 +3461,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3576,6 +3611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4316,6 +4356,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4609,6 +4654,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5349,6 +5399,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5494,6 +5549,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6234,6 +6294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6379,6 +6444,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7267,6 +7337,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7412,6 +7487,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8152,6 +8232,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8297,6 +8382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9037,6 +9127,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9182,6 +9277,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10070,6 +10170,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10215,6 +10320,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10955,6 +11065,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11100,6 +11215,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11840,6 +11960,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12133,6 +12258,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12873,6 +13003,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13018,6 +13153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13758,6 +13898,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13903,6 +14048,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14643,6 +14793,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14936,6 +15091,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15676,6 +15836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15821,6 +15986,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16561,6 +16731,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16706,6 +16881,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17446,6 +17626,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17739,6 +17924,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18479,6 +18669,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18624,6 +18819,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19364,6 +19564,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19509,6 +19714,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20397,6 +20607,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20542,6 +20757,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21282,6 +21502,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21427,6 +21652,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22167,6 +22397,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22312,6 +22547,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23200,6 +23440,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23345,6 +23590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24085,6 +24335,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24230,6 +24485,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24970,6 +25230,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25115,6 +25380,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26003,6 +26273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26148,6 +26423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26888,6 +27168,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27033,6 +27318,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27773,6 +28063,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27918,6 +28213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28806,6 +29106,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28951,6 +29256,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29691,6 +30001,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29836,6 +30151,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30576,6 +30896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30869,6 +31194,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31609,6 +31939,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31754,6 +32089,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32494,6 +32834,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32639,6 +32984,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33379,6 +33729,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33672,6 +34027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34412,6 +34772,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34557,6 +34922,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35297,6 +35667,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35442,6 +35817,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36182,6 +36562,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36327,6 +36712,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37215,6 +37605,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37360,6 +37755,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38100,6 +38500,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38245,6 +38650,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38985,6 +39395,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39278,6 +39693,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40018,6 +40438,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40163,6 +40588,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40903,6 +41333,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41048,6 +41483,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41936,6 +42376,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42081,6 +42526,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42821,6 +43271,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42966,6 +43421,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43706,6 +44166,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43851,6 +44316,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44739,6 +45209,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44884,6 +45359,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45624,6 +46104,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45769,6 +46254,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46509,6 +46999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46802,6 +47297,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47394,6 +47894,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47687,6 +48192,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48427,6 +48937,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48572,6 +49087,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49312,6 +49832,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49457,6 +49982,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50345,6 +50875,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO338" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50490,6 +51025,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51230,6 +51770,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51375,6 +51920,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52115,6 +52665,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52260,6 +52815,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53148,6 +53708,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO357" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53293,6 +53858,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO358" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54033,6 +54603,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO363" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54178,6 +54753,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54918,6 +55498,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO369" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55211,6 +55796,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55951,6 +56541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO376" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56094,6 +56689,11 @@
       <c r="S377" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO377" t="inlineStr">
